--- a/output/enforcement/非诉表格.xlsx
+++ b/output/enforcement/非诉表格.xlsx
@@ -112,7 +112,7 @@
     <t>（2025）粤 7101 行审 3355 号</t>
   </si>
   <si>
-    <t>向宏/梅文静</t>
+    <t>梅文静</t>
   </si>
   <si>
     <t>二〇二五年四月二十八日</t>
